--- a/cases/AConly_case118_psse.xlsx
+++ b/cases/AConly_case118_psse.xlsx
@@ -15150,7 +15150,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K2" t="n">
         <v>1e-06</v>
@@ -15197,7 +15197,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K3" t="n">
         <v>1e-06</v>
@@ -15244,7 +15244,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K4" t="n">
         <v>1e-06</v>
@@ -15291,7 +15291,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K5" t="n">
         <v>1e-06</v>
@@ -15338,7 +15338,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K6" t="n">
         <v>1e-06</v>
@@ -15385,7 +15385,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K7" t="n">
         <v>1e-06</v>
@@ -15432,7 +15432,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K8" t="n">
         <v>1e-06</v>
@@ -15479,7 +15479,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K9" t="n">
         <v>1e-06</v>
@@ -15526,7 +15526,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
         <v>1e-06</v>
@@ -15573,7 +15573,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K11" t="n">
         <v>1e-06</v>
@@ -15620,7 +15620,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K12" t="n">
         <v>1e-06</v>
@@ -15667,7 +15667,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K13" t="n">
         <v>1e-06</v>
@@ -15714,7 +15714,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K14" t="n">
         <v>1e-06</v>
@@ -15761,7 +15761,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K15" t="n">
         <v>1e-06</v>
@@ -15808,7 +15808,7 @@
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K16" t="n">
         <v>1e-06</v>
@@ -15855,7 +15855,7 @@
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K17" t="n">
         <v>1e-06</v>
@@ -15902,7 +15902,7 @@
         <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K18" t="n">
         <v>1e-06</v>
@@ -15949,7 +15949,7 @@
         <v>1</v>
       </c>
       <c r="J19" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K19" t="n">
         <v>1e-06</v>
@@ -15996,7 +15996,7 @@
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K20" t="n">
         <v>1e-06</v>
@@ -16043,7 +16043,7 @@
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K21" t="n">
         <v>1e-06</v>
@@ -16090,7 +16090,7 @@
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K22" t="n">
         <v>1e-06</v>
@@ -16137,7 +16137,7 @@
         <v>1</v>
       </c>
       <c r="J23" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K23" t="n">
         <v>1e-06</v>
@@ -16184,7 +16184,7 @@
         <v>1</v>
       </c>
       <c r="J24" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K24" t="n">
         <v>1e-06</v>
@@ -16231,7 +16231,7 @@
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K25" t="n">
         <v>1e-06</v>
@@ -16278,7 +16278,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K26" t="n">
         <v>1e-06</v>
@@ -16325,7 +16325,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K27" t="n">
         <v>1e-06</v>
@@ -16372,7 +16372,7 @@
         <v>1</v>
       </c>
       <c r="J28" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K28" t="n">
         <v>1e-06</v>
@@ -16419,7 +16419,7 @@
         <v>1</v>
       </c>
       <c r="J29" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K29" t="n">
         <v>1e-06</v>
@@ -16466,7 +16466,7 @@
         <v>1</v>
       </c>
       <c r="J30" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K30" t="n">
         <v>1e-06</v>
@@ -16513,7 +16513,7 @@
         <v>1</v>
       </c>
       <c r="J31" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K31" t="n">
         <v>1e-06</v>
@@ -16560,7 +16560,7 @@
         <v>1</v>
       </c>
       <c r="J32" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K32" t="n">
         <v>1e-06</v>
@@ -16607,7 +16607,7 @@
         <v>1</v>
       </c>
       <c r="J33" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K33" t="n">
         <v>1e-06</v>
@@ -16654,7 +16654,7 @@
         <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K34" t="n">
         <v>1e-06</v>
@@ -16701,7 +16701,7 @@
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K35" t="n">
         <v>1e-06</v>
@@ -16748,7 +16748,7 @@
         <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K36" t="n">
         <v>1e-06</v>
@@ -16795,7 +16795,7 @@
         <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K37" t="n">
         <v>1e-06</v>
@@ -16842,7 +16842,7 @@
         <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K38" t="n">
         <v>1e-06</v>
@@ -16889,7 +16889,7 @@
         <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K39" t="n">
         <v>1e-06</v>
@@ -16936,7 +16936,7 @@
         <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K40" t="n">
         <v>1e-06</v>
@@ -16983,7 +16983,7 @@
         <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K41" t="n">
         <v>1e-06</v>
@@ -17030,7 +17030,7 @@
         <v>1</v>
       </c>
       <c r="J42" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K42" t="n">
         <v>1e-06</v>
@@ -17077,7 +17077,7 @@
         <v>1</v>
       </c>
       <c r="J43" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K43" t="n">
         <v>1e-06</v>
@@ -17124,7 +17124,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K44" t="n">
         <v>1e-06</v>
@@ -17171,7 +17171,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K45" t="n">
         <v>1e-06</v>
@@ -17218,7 +17218,7 @@
         <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K46" t="n">
         <v>1e-06</v>
@@ -17265,7 +17265,7 @@
         <v>1</v>
       </c>
       <c r="J47" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K47" t="n">
         <v>1e-06</v>
@@ -17312,7 +17312,7 @@
         <v>1</v>
       </c>
       <c r="J48" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K48" t="n">
         <v>1e-06</v>
@@ -17359,7 +17359,7 @@
         <v>1</v>
       </c>
       <c r="J49" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K49" t="n">
         <v>1e-06</v>
@@ -17406,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K50" t="n">
         <v>1e-06</v>
@@ -17453,7 +17453,7 @@
         <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K51" t="n">
         <v>1e-06</v>
@@ -17500,7 +17500,7 @@
         <v>1</v>
       </c>
       <c r="J52" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K52" t="n">
         <v>1e-06</v>
@@ -17547,7 +17547,7 @@
         <v>1</v>
       </c>
       <c r="J53" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K53" t="n">
         <v>1e-06</v>
@@ -17594,7 +17594,7 @@
         <v>1</v>
       </c>
       <c r="J54" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K54" t="n">
         <v>1e-06</v>
@@ -17641,7 +17641,7 @@
         <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>100000000</v>
+        <v>100</v>
       </c>
       <c r="K55" t="n">
         <v>1e-06</v>
